--- a/Q_and_A/taylor_swift_QandA.xlsx
+++ b/Q_and_A/taylor_swift_QandA.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="292">
   <si>
     <t>Question</t>
   </si>
@@ -202,7 +202,7 @@
     <t>Taylor Swift 的第9个冠军单曲是？</t>
   </si>
   <si>
-    <t>反英雄</t>
+    <t>Anti-Hero</t>
   </si>
   <si>
     <t>Taylor Swift 获得了几次格莱美年度专辑大奖？</t>
@@ -217,9 +217,6 @@
     <t>Taylor Swift 在 Billboard Hot 100 在榜最久的歌是？</t>
   </si>
   <si>
-    <t>Anti-Hero</t>
-  </si>
-  <si>
     <t>Taylor Swift 哪两年同时拿了两首美国 billboard hot100 冠单？</t>
   </si>
   <si>
@@ -686,6 +683,228 @@
   </si>
   <si>
     <t>champagne problems</t>
+  </si>
+  <si>
+    <t>哪张充满魔力的专辑收录了迷人的歌曲 "Mary's Song"，连仙女教母都会跟着哼唱？</t>
+  </si>
+  <si>
+    <t>Taylor Swift</t>
+  </si>
+  <si>
+    <t>Taylor Swift 的哪张专辑因 Snow Patrol 的 Gary Lightbody 加入而增添了摇滚色彩，使其成为霸榜的派对混音之作？</t>
+  </si>
+  <si>
+    <t>哪张炽热的专辑包含了叛逆颂歌 "Picture to Burn"，让每一个前任都三思而后行？</t>
+  </si>
+  <si>
+    <t>猜猜 Taylor Swift 的哪首热门歌曲用“She's cheer captain and I'm on the bleachers”这句歌词完美诠释了高中梦想氛围，深受所有逆袭者的喜爱？</t>
+  </si>
+  <si>
+    <t>收录了暖心曲调 "Tied Together with a Smile"、堪称阴霾天完美良方的专辑叫什么名字？</t>
+  </si>
+  <si>
+    <t>还记得那首开启巨星之路的押韵谜题吗？年轻的 Taylor Swift 凭借哪首诗赢得了全国诗歌比赛冠军？</t>
+  </si>
+  <si>
+    <t>Monster in My Closet</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在 "Hope for Haiti" 专辑中献声演唱了哪首振奋人心的曲目，证明即使心碎也能点燃希望？</t>
+  </si>
+  <si>
+    <t>Breathless</t>
+  </si>
+  <si>
+    <t>凭借巧妙的歌词创作，Taylor Swift 靠哪首朗朗上口的歌曲摘得了2015年 iHeartRadio Music Awards 的“最佳歌词”桂冠？</t>
+  </si>
+  <si>
+    <t>Taylor Swift 首张专辑中让乡村乐迷一听到节拍就高呼“Yeehaw!”的首支单曲是什么？</t>
+  </si>
+  <si>
+    <t>Taylor Swift 从日记中借用了哪位儿时闺蜜的名字来创作热单 "Fifteen"，唤起了我们对黄金校园时光的回忆？</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>哪张专辑于2012年以火热色调重磅发布，首周销量突破百万，证明了 Red 确实是成功的颜色？</t>
+  </si>
+  <si>
+    <t>在 Taylor Swift 的哪张璀璨专辑中，宁静的曲目 "Clean" 作为收尾曲，宛如狂欢派对后清凉的夜晚？</t>
+  </si>
+  <si>
+    <t>哪张唱片充满了流行魔力以及 "Style" 和 "Out of the Woods" 等破纪录热单，是对现代流行完美的极致致敬？</t>
+  </si>
+  <si>
+    <t>Taylor Swift 为高中才艺表演写了哪首奇特又真挚的歌曲，为她日后的一夜成名奠定了基础？</t>
+  </si>
+  <si>
+    <t>Our Song</t>
+  </si>
+  <si>
+    <t>哪张开创性的专辑让 Taylor Swift 成为首位两度获得格莱美年度专辑奖的女性，同时还带给我们难忘的80年代风情？</t>
+  </si>
+  <si>
+    <t>谁在 "Bad Blood" MV 中饰演 Lucky，为动作场面增添了一抹独立魅力？</t>
+  </si>
+  <si>
+    <t>Lena Dunham</t>
+  </si>
+  <si>
+    <t>哪位电视剧医生在 "Bad Blood" MV 中客串 Luna，带来酷炫的氛围？</t>
+  </si>
+  <si>
+    <t>Ellen Pompeo</t>
+  </si>
+  <si>
+    <t>谁在 "Bad Blood" MV 中扮演 Domino，为画面注入了好莱坞 glamour？</t>
+  </si>
+  <si>
+    <t>Jessica Alba</t>
+  </si>
+  <si>
+    <t>谁是分手颂歌 "I Knew You Were Trouble" 背后的灵感缪斯，最终被取代了地位？</t>
+  </si>
+  <si>
+    <t>Harry Styles</t>
+  </si>
+  <si>
+    <t>Taylor Swift 与 Joe Jonas 的旋风恋情在哪一年登上了小报头条？</t>
+  </si>
+  <si>
+    <t>Taylor Swift 与好莱坞当红男星 Jake Gyllenhaal 的热烈故事发生在什么时候？</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在2010年的哪部浪漫喜剧中惊喜客串，迷倒了所有观众？</t>
+  </si>
+  <si>
+    <t>Valentine's Day</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在哪首歌中吟唱了双手并用的爱情——一只手握着方向盘，另一只手放在心上？</t>
+  </si>
+  <si>
+    <t>哪首热单宣称高跟鞋和运动鞋各自诉说着独特的爱情故事？</t>
+  </si>
+  <si>
+    <t>哪首歌包含了“I guess you didn't care, and I guess I liked that”这句自白式歌词，传递出苦乐参半的真相？</t>
+  </si>
+  <si>
+    <t>I Knew You Were Trouble</t>
+  </si>
+  <si>
+    <t>在哪个MV中，Taylor Swift 用一个戏剧性的电话结束了恋情，让我们不禁潸然泪下？</t>
+  </si>
+  <si>
+    <t>哪个MV展现了 Taylor Swift 通过电话告别，标志着一段苦乐参半恋情的终结？</t>
+  </si>
+  <si>
+    <t>Swift 在哪部剧集中完成了她的演艺处女作，踏上了犯罪侦破的舞台？</t>
+  </si>
+  <si>
+    <t>CSI</t>
+  </si>
+  <si>
+    <t>Taylor Swift 获得过几次金球奖提名，证明了她在银幕和音乐上的双重星光？</t>
+  </si>
+  <si>
+    <t>Twice</t>
+  </si>
+  <si>
+    <t>Taylor Swift 何时以单曲 "Tim McGraw" 开启了她的音乐旅程，让乡村乐迷欣喜若狂？</t>
+  </si>
+  <si>
+    <t>年轻时，Taylor Swift 在才艺表演中大放异彩，获得了为哪位标志性歌手开场的机会，为未来的星途铺平了道路？</t>
+  </si>
+  <si>
+    <t>Charlie Daniels</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在2018年开启的激动人心的巡演叫什么名字，将体育场变成了盛大的 Swiftie 派对区？</t>
+  </si>
+  <si>
+    <t>Taylor Swift's Reputation Stadium Tour</t>
+  </si>
+  <si>
+    <t>根据 Forbes 的数据，截至2018年8月，Taylor Swift 令人瞠目的净资产是多少，这个数字甚至让黑粉们都大吃一惊？</t>
+  </si>
+  <si>
+    <t>$320 million</t>
+  </si>
+  <si>
+    <t>在2008年的 Me and My Gang Tour 中，Taylor Swift 为哪个音乐组合担任开场嘉宾，一路俘获观众芳心？</t>
+  </si>
+  <si>
+    <t>Rascal Flatts</t>
+  </si>
+  <si>
+    <t>到2015年初，Taylor Swift 在全球卖出了多少张专辑，巩固了她打破纪录的天后地位？</t>
+  </si>
+  <si>
+    <t>40 million</t>
+  </si>
+  <si>
+    <t>在 "Bad Blood" MV 中，谁演绎了凶猛的化身 Slay Z，为MV魔法增添了T台级别的风采？</t>
+  </si>
+  <si>
+    <t>Gigi Hadid</t>
+  </si>
+  <si>
+    <t>14岁的 Taylor Swift 曾就读于哪所学校，将高中生活与未来的霸榜热单融为一体？</t>
+  </si>
+  <si>
+    <t>Hendersonville High School</t>
+  </si>
+  <si>
+    <t>在那个令人难忘的 MTV 时刻，当 Kanye 打断她的获奖感言时，Taylor Swift 凭借无可置疑的气场拿下了哪个奖项？</t>
+  </si>
+  <si>
+    <t>Best Female Video</t>
+  </si>
+  <si>
+    <t>Taylor Swift 是以哪位音乐传奇人物的名字命名的，注定她生来就与和谐旋律结缘？</t>
+  </si>
+  <si>
+    <t>James Taylor</t>
+  </si>
+  <si>
+    <t>1989 World Tour 于哪个史诗般的日期拉开帷幕，开启了这场至今仍被粉丝庆祝的流行盛宴？</t>
+  </si>
+  <si>
+    <t>May 5th, 2015</t>
+  </si>
+  <si>
+    <t>在她早期崭露头角的模特生涯中，Taylor Swift 为 Abercrombie and Fitch 的哪个活动担任模特？</t>
+  </si>
+  <si>
+    <t>Rising Stars</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在哪部温馨电影的片场遇到了演员 Taylor Lautner，这段邂逅至今仍被粉丝们津津乐道？</t>
+  </si>
+  <si>
+    <t>哪部电影的原声带中收录了两首由 Taylor 创作的耀眼曲目，为大银幕增添了音乐色彩？</t>
+  </si>
+  <si>
+    <t>Hannah Montana: The Movie</t>
+  </si>
+  <si>
+    <t>哪位吉他导师引领 Taylor 走进了音乐殿堂，为她日后的歌词天赋奠定了基础？</t>
+  </si>
+  <si>
+    <t>Ronnie Cremer</t>
+  </si>
+  <si>
+    <t>Taylor Swift 在2014年12月庆祝了多少岁生日，证明25岁只是辉煌的开始？</t>
+  </si>
+  <si>
+    <t>在哪首经典热单中，Taylor 唱出了“Marry me Juliet you'll never have to be alone”这句深情歌词，奠定了她作为现代吟游诗人的地位？</t>
+  </si>
+  <si>
+    <t>年仅11岁时，Taylor Swift 为哪支职业运动队演唱国歌惊艳全场，展现了她早期的明星潜质？</t>
+  </si>
+  <si>
+    <t>Philadelphia 76ers</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1528,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1333,6 +1552,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1645,7 +1867,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="8.63636363636364" style="1" customWidth="1"/>
@@ -1921,164 +2143,164 @@
         <v>61</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" ht="112" spans="1:2">
       <c r="A35" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="36" ht="84" spans="1:2">
       <c r="A36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="37" ht="56" spans="1:2">
       <c r="A37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="38" ht="98" spans="1:2">
       <c r="A38" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="39" ht="98" spans="1:2">
       <c r="A39" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="40" ht="70" spans="1:2">
       <c r="A40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="41" ht="98" spans="1:2">
       <c r="A41" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="42" ht="98" spans="1:2">
       <c r="A42" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="43" ht="70" spans="1:2">
       <c r="A43" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="44" ht="70" spans="1:2">
       <c r="A44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="45" ht="70" spans="1:2">
       <c r="A45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="46" ht="70" spans="1:2">
       <c r="A46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="47" ht="70" spans="1:2">
       <c r="A47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="48" ht="98" spans="1:2">
       <c r="A48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="49" ht="98" spans="1:2">
       <c r="A49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="50" ht="126" spans="1:2">
       <c r="A50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="51" ht="154" spans="1:2">
       <c r="A51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="52" ht="210" spans="1:2">
       <c r="A52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="53" ht="70" spans="1:2">
       <c r="A53" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="54" ht="126" spans="1:2">
       <c r="A54" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="3">
         <v>20</v>
@@ -2086,23 +2308,23 @@
     </row>
     <row r="55" ht="98" spans="1:2">
       <c r="A55" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="56" ht="56" spans="1:2">
       <c r="A56" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="57" ht="70" spans="1:2">
       <c r="A57" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B57" s="3">
         <v>2006</v>
@@ -2110,7 +2332,7 @@
     </row>
     <row r="58" ht="70" spans="1:2">
       <c r="A58" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" s="5">
         <v>38887</v>
@@ -2118,23 +2340,23 @@
     </row>
     <row r="59" ht="70" spans="1:2">
       <c r="A59" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="60" ht="84" spans="1:2">
       <c r="A60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="61" ht="98" spans="1:2">
       <c r="A61" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B61" s="3">
         <v>10</v>
@@ -2142,7 +2364,7 @@
     </row>
     <row r="62" ht="98" spans="1:2">
       <c r="A62" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B62" s="3">
         <v>1989</v>
@@ -2150,15 +2372,15 @@
     </row>
     <row r="63" ht="42" spans="1:2">
       <c r="A63" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="64" ht="56" spans="1:2">
       <c r="A64" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B64" s="3">
         <v>2019</v>
@@ -2166,7 +2388,7 @@
     </row>
     <row r="65" ht="98" spans="1:2">
       <c r="A65" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3">
         <v>6</v>
@@ -2174,7 +2396,7 @@
     </row>
     <row r="66" ht="112" spans="1:2">
       <c r="A66" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B66" s="6">
         <v>1989</v>
@@ -2182,7 +2404,7 @@
     </row>
     <row r="67" ht="98" spans="1:2">
       <c r="A67" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B67" s="7">
         <v>43049</v>
@@ -2190,7 +2412,7 @@
     </row>
     <row r="68" ht="70" spans="1:2">
       <c r="A68" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B68" s="6">
         <v>10</v>
@@ -2198,15 +2420,15 @@
     </row>
     <row r="69" ht="70" spans="1:2">
       <c r="A69" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="70" ht="84" spans="1:2">
       <c r="A70" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B70" s="7">
         <v>41870</v>
@@ -2214,319 +2436,319 @@
     </row>
     <row r="71" ht="70" spans="1:2">
       <c r="A71" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="72" ht="112" spans="1:2">
       <c r="A72" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="73" ht="126" spans="1:2">
       <c r="A73" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="74" ht="154" spans="1:2">
       <c r="A74" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="75" ht="56" spans="1:2">
       <c r="A75" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="76" ht="126" spans="1:2">
       <c r="A76" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="77" ht="168" spans="1:2">
       <c r="A77" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="78" ht="154" spans="1:2">
       <c r="A78" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="79" ht="182" spans="1:2">
       <c r="A79" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="80" ht="210" spans="1:2">
       <c r="A80" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="81" ht="252" spans="1:2">
       <c r="A81" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="82" ht="140" spans="1:2">
       <c r="A82" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="83" ht="154" spans="1:2">
       <c r="A83" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="84" ht="210" spans="1:2">
       <c r="A84" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" ht="168" spans="1:2">
       <c r="A85" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="86" ht="168" spans="1:2">
       <c r="A86" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="87" ht="112" spans="1:2">
       <c r="A87" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" ht="126" spans="1:2">
       <c r="A88" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89" ht="112" spans="1:2">
       <c r="A89" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" ht="182" spans="1:2">
       <c r="A90" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="91" ht="182" spans="1:2">
       <c r="A91" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="92" ht="182" spans="1:2">
       <c r="A92" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="93" ht="224" spans="1:2">
       <c r="A93" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="94" ht="266" spans="1:2">
       <c r="A94" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="95" ht="266" spans="1:2">
       <c r="A95" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="96" ht="224" spans="1:2">
       <c r="A96" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="97" ht="238" spans="1:2">
       <c r="A97" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="98" ht="252" spans="1:2">
       <c r="A98" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="99" ht="224" spans="1:2">
       <c r="A99" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="100" ht="196" spans="1:2">
       <c r="A100" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="101" ht="210" spans="1:2">
       <c r="A101" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B101" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="102" ht="182" spans="1:2">
       <c r="A102" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="103" ht="210" spans="1:2">
       <c r="A103" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" ht="210" spans="1:2">
       <c r="A104" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B104" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="105" ht="252" spans="1:2">
       <c r="A105" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B105" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="106" ht="294" spans="1:2">
       <c r="A106" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="107" ht="224" spans="1:2">
       <c r="A107" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B107" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="108" ht="238" spans="1:2">
       <c r="A108" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B108" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="109" ht="210" spans="1:2">
       <c r="A109" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="110" ht="182" spans="1:2">
       <c r="A110" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>60</v>
@@ -2534,90 +2756,466 @@
     </row>
     <row r="111" ht="238" spans="1:2">
       <c r="A111" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B111" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="112" ht="266" spans="1:2">
       <c r="A112" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="113" ht="168" spans="1:2">
       <c r="A113" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="114" ht="210" spans="1:2">
       <c r="A114" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" ht="210" spans="1:2">
       <c r="A115" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B115" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="116" ht="252" spans="1:2">
       <c r="A116" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B116" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="117" ht="294" spans="1:2">
       <c r="A117" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B117" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="118" ht="280" spans="1:2">
       <c r="A118" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="119" ht="308" spans="1:2">
       <c r="A119" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="120" ht="238" spans="1:2">
       <c r="A120" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="121" ht="224" spans="1:2">
       <c r="A121" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B121" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B121" s="6" t="s">
+    </row>
+    <row r="122" ht="140" spans="1:2">
+      <c r="A122" s="8" t="s">
         <v>218</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="123" ht="196" spans="1:2">
+      <c r="A123" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="124" ht="154" spans="1:2">
+      <c r="A124" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="125" ht="266" spans="1:2">
+      <c r="A125" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="126" ht="154" spans="1:2">
+      <c r="A126" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="127" ht="168" spans="1:2">
+      <c r="A127" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="128" ht="182" spans="1:2">
+      <c r="A128" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="129" ht="224" spans="1:2">
+      <c r="A129" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="130" ht="154" spans="1:2">
+      <c r="A130" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="131" ht="182" spans="1:2">
+      <c r="A131" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="132" ht="154" spans="1:2">
+      <c r="A132" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="133" ht="182" spans="1:2">
+      <c r="A133" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B133" s="8">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="134" ht="196" spans="1:2">
+      <c r="A134" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B134" s="8">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="135" ht="154" spans="1:2">
+      <c r="A135" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="136" ht="196" spans="1:2">
+      <c r="A136" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B136" s="8">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="137" ht="140" spans="1:2">
+      <c r="A137" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="138" ht="126" spans="1:2">
+      <c r="A138" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="139" ht="154" spans="1:2">
+      <c r="A139" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="140" ht="140" spans="1:2">
+      <c r="A140" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="141" ht="112" spans="1:2">
+      <c r="A141" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B141" s="8">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="142" ht="140" spans="1:2">
+      <c r="A142" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B142" s="8">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="143" ht="112" spans="1:2">
+      <c r="A143" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="144" ht="154" spans="1:2">
+      <c r="A144" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="145" ht="98" spans="1:2">
+      <c r="A145" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="146" ht="210" spans="1:2">
+      <c r="A146" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="147" ht="140" spans="1:2">
+      <c r="A147" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="148" ht="140" spans="1:2">
+      <c r="A148" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="149" ht="112" spans="1:2">
+      <c r="A149" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="150" ht="126" spans="1:2">
+      <c r="A150" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="151" ht="140" spans="1:2">
+      <c r="A151" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B151" s="8">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="152" ht="182" spans="1:2">
+      <c r="A152" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="153" ht="168" spans="1:2">
+      <c r="A153" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="154" ht="196" spans="1:2">
+      <c r="A154" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="155" ht="196" spans="1:2">
+      <c r="A155" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="156" ht="154" spans="1:2">
+      <c r="A156" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="157" ht="154" spans="1:2">
+      <c r="A157" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="158" ht="140" spans="1:2">
+      <c r="A158" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="159" ht="196" spans="1:2">
+      <c r="A159" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="160" ht="140" spans="1:2">
+      <c r="A160" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="161" ht="168" spans="1:2">
+      <c r="A161" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="162" ht="168" spans="1:2">
+      <c r="A162" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="163" ht="182" spans="1:2">
+      <c r="A163" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="164" ht="140" spans="1:2">
+      <c r="A164" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="165" ht="126" spans="1:2">
+      <c r="A165" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="166" ht="126" spans="1:2">
+      <c r="A166" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B166" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" ht="266" spans="1:2">
+      <c r="A167" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="168" ht="154" spans="1:2">
+      <c r="A168" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
